--- a/dataset/v2/piping_progress.xlsx
+++ b/dataset/v2/piping_progress.xlsx
@@ -544,12 +544,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PIP-DRY-1515</t>
+          <t>PIP-BLT-1324</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2"-P-2301-A6A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air blowing and drying, instrument air header</t>
+          <t>Bolt torque and gasket joint assembly, Unit 2 manifold</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -569,24 +569,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Substation</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11/11/2026</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -617,17 +612,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15/Jun/2026</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -640,7 +630,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PIP-ERC-1305</t>
+          <t>PIP-ERC-1302</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +645,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rack erection, Module 3 tier 1, flare header 18"-P-1301-B7A and utilit</t>
+          <t>Erect rack steel, Module 3 (Ch 80-110)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -665,35 +655,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24/Jun/2026</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>27/Jun/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PIP-ERC-1311</t>
+          <t>PIP-ERC-1304</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24"-P-1001-A1A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -703,7 +693,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erect Line 24"-P-1001-A1A, Unit 2 rack</t>
+          <t>Pipe rack erection, crude header, Unit 2 to tank farm</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -713,35 +703,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PIP-ERC-1315</t>
+          <t>PIP-ERC-1311</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16"-P-1002-A1A</t>
+          <t>24"-P-1001-A1A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -751,7 +741,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erect line 16"-P-1002-A1A, gas service, Unit 1 manifold</t>
+          <t>Erect Line 24"-P-1001-A1A, Unit 2 rack</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -759,37 +749,32 @@
           <t>PIP</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Manifold</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28/11/2026</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="J9" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PIP-ERC-1316</t>
+          <t>PIP-ERC-1312</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12"-P-1003-A5A</t>
+          <t>24"-P-1001-A1A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -799,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erect line 12"-P-1003-A5A, test separator loop</t>
+          <t>Erect crude header 24"-P-1001-A1A, tank farm approach</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -809,35 +794,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>05/Nov/2026</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PIP-ERC-1330</t>
+          <t>PIP-ERC-1315</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18"-P-1301-B7A</t>
+          <t>16"-P-1002-A1A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -847,7 +832,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erect flare header 18"-P-1301-B7A, manifold to KO drum</t>
+          <t>Erect line 16"-P-1002-A1A, gas service, Unit 1 manifold</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -857,35 +842,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>28/11/2026</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="J11" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIP-ERC-1333</t>
+          <t>PIP-ERC-1316</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6"-P-1302-A6A</t>
+          <t>12"-P-1003-A5A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -895,7 +880,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erect blowdown lines 6"-P-1302-A6A, wellhead SDVs</t>
+          <t>Erect line 12"-P-1003-A5A, test separator loop</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -905,35 +890,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PIP-ERC-1334</t>
+          <t>PIP-ERC-1317</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4"-P-1303-C5B</t>
+          <t>8"-P-1004-A6A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -943,7 +928,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erect drain header 4"-P-1303-C5B, closed drain</t>
+          <t>Erect line 8"-P-1004-A6A, glycol feed to contactor V-1201</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -953,35 +938,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J13" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIP-ERC-1341</t>
+          <t>PIP-ERC-1322</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P-1401A</t>
+          <t>10"-P-2002-A5A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -991,7 +976,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Suction and discharge piping, pumps P-1401A/B to manifold</t>
+          <t>Erect line 10"-P-2002-A5A, test header Unit 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1001,35 +986,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PIP-ERC-1343</t>
+          <t>PIP-ERC-1330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3"-P-2104-C5B</t>
+          <t>18"-P-1301-B7A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1039,7 +1024,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Install tank dewatering lines 3"-P-2104-C5B</t>
+          <t>Erect flare header 18"-P-1301-B7A, manifold to KO drum</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1054,30 +1039,30 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>25/Aug/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15/Jun/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PIP-FAB-1310</t>
+          <t>PIP-ERC-1331</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24"-P-1001-A1A</t>
+          <t>FST-1301</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1087,7 +1072,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shop fabrication, 24"-P-1001-A1A spools</t>
+          <t>Erect flare header riser, FST-1301 to tip</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1097,35 +1082,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/Oct/2026</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13/Oct/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PIP-FLS-1514</t>
+          <t>PIP-ERC-1351</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3"-P-2302-A6A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1135,7 +1120,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Flush, dry and reinstate, test packs 1-3</t>
+          <t>Nitrogen line 3"-P-2302-A6A, package to header</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1150,25 +1135,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15/Nov/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PIP-HLT-1325</t>
+          <t>PIP-ERC-1354</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20"-P-2001-A1A</t>
+          <t>1"-P-2501-A6A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1178,7 +1163,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pipe supports and guides, Unit 2 rack stretch</t>
+          <t>Chemical injection piping 1"-P-2501-A6A, skids to injection points</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1188,35 +1173,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26/Oct/2026</t>
+          <t>04/Jul/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>07/Jul/2026</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PIP-HYT-1511</t>
+          <t>PIP-FAB-1310</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24"-P-1001-A1A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1226,7 +1211,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hydrotest package 2, Unit 2 header 20"-P-2001-A1A</t>
+          <t>Shop fabrication, 24"-P-1001-A1A spools</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1236,35 +1221,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manifold</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12/11/2026</t>
+          <t>13/Oct/2026</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PIP-HYT-1512</t>
+          <t>PIP-FLS-1514</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18"-P-1301-B7A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1274,7 +1259,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pneumatic leak test with nitrogen, flare header</t>
+          <t>Flush, dry and reinstate, test packs 1-3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1284,25 +1269,30 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>02/Nov/2026</t>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>15/11/2026</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PIP-INS-1319</t>
+          <t>PIP-HYT-1510</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1317,7 +1307,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Install restriction orifice spools and sampling connections, Unit 1</t>
+          <t>Hydrotest package 1, Unit 1 lines 16"-P-1002-A1A and 12"-P-1003-A5A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1327,30 +1317,30 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>01/11/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28/11/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PIP-UGS-1156</t>
+          <t>PIP-HYT-1511</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1365,7 +1355,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Chamber and catch pit construction, OWS outfall</t>
+          <t>Hydrotest package 2, Unit 2 header 20"-P-2001-A1A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1375,17 +1365,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>12/11/2026</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1398,12 +1388,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PIP-UGS-1170</t>
+          <t>PIP-HYT-1512</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10"-P-1602-B1A</t>
+          <t>18"-P-1301-B7A</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1413,7 +1403,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Trenching for firewater ring main 10"-P-1602-B1A, Unit 1 and manifold</t>
+          <t>Pneumatic leak test with nitrogen, flare header</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1423,30 +1413,30 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>02/11/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>16/Apr/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>480</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>480</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PIP-UGS-1172</t>
+          <t>PIP-UGS-1170</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1456,12 +1446,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hydrotest firewater main 10"-P-1602-B1A, Manifold to Unit 1 section</t>
+          <t>Trenching for firewater ring main 10"-P-1602-B1A, Unit 1 and manifold</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1471,30 +1461,30 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="J24" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PIP-UGS-1173</t>
+          <t>PIP-UGS-1171</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1504,12 +1494,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hydrotest firewater main 10"-P-1602-B1A, Unit 1 to Unit 2 section</t>
+          <t>Lay and joint GRP firewater main 10"-P-1602-B1A</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1519,30 +1509,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manifold</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="J25" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PIP-UGS-1174</t>
+          <t>PIP-UGS-1172</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1552,12 +1542,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Backfill and compaction, firewater trench 10"-P-1602-B1A</t>
+          <t>Hydrotest firewater main 10"-P-1602-B1A, Manifold to Unit 1 section</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1567,24 +1557,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manifold</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="J26" t="n">
-        <v>480</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
@@ -1615,7 +1600,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1625,7 +1610,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1663,7 +1648,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1673,7 +1658,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1686,7 +1671,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PIP-WLD-1332</t>
+          <t>PIP-WLD-1323</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1701,7 +1686,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Alloy weld and PMI, flare header, welds 20-31</t>
+          <t>Field weld and RT, Unit 2 header welds 19-34</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1711,19 +1696,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1754,7 +1739,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
